--- a/media/exports/services-sample-statements.xlsx
+++ b/media/exports/services-sample-statements.xlsx
@@ -1038,7 +1038,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1428,7 +1428,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2086,7 +2086,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2549,7 +2549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2984,7 +2984,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3912,7 +3912,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5206,7 +5206,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:45am</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:45am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 services-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
